--- a/healthcare_assessment_forms/025_voice_tremor_assessment_form--healthcare_assessment_forms.xlsx
+++ b/healthcare_assessment_forms/025_voice_tremor_assessment_form--healthcare_assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -638,12 +638,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -671,12 +671,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'mild',_'value':_1}</t>
+          <t>mild</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Mild', 'value': 1}</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -688,12 +688,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'moderate',_'value':_2}</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Moderate', 'value': 2}</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -705,12 +705,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'severe',_'value':_3}</t>
+          <t>severe</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Severe', 'value': 3}</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -722,12 +722,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all',_'value':_1}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Not at all', 'value': 1}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
@@ -739,12 +739,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'a_lot',_'value':_2}</t>
+          <t>a_lot</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'A lot', 'value': 2}</t>
+          <t>A lot</t>
         </is>
       </c>
     </row>
@@ -756,12 +756,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'a_moderate_amount',_'value':_3}</t>
+          <t>a_moderate_amount</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'A moderate amount', 'value': 3}</t>
+          <t>A moderate amount</t>
         </is>
       </c>
     </row>
@@ -773,29 +773,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'a_lot',_'value':_4}</t>
+          <t>a_small_amount</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'A lot', 'value': 4}</t>
+          <t>A small amount</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>daily_impact_choices</t>
+          <t>voice_sample_uploads_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'a_small_amount',_'value':_5}</t>
+          <t>upload_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'A small amount', 'value': 5}</t>
+          <t>Upload 1</t>
         </is>
       </c>
     </row>
@@ -807,27 +807,10 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'upload_1',_'value':_1}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
-        <is>
-          <t>{'label': 'Upload 1', 'value': 1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>voice_sample_uploads_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
